--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aeu.00037_19470820.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="aeu.00037_19470820.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.8.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -959,7 +959,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
